--- a/data/H131_20260624_18.xlsx
+++ b/data/H131_20260624_18.xlsx
@@ -2383,13 +2383,13 @@
         <v>1024.0</v>
       </c>
       <c r="O29" s="2">
-        <v>387.0</v>
+        <v>411.0</v>
       </c>
       <c r="P29" s="2">
         <v>422.0</v>
       </c>
       <c r="Q29" s="2">
-        <v>215.0</v>
+        <v>191.0</v>
       </c>
       <c r="R29" s="2">
         <v>47.0</v>
@@ -2596,13 +2596,13 @@
         <v>1097.0</v>
       </c>
       <c r="O32" s="2">
-        <v>536.0</v>
+        <v>537.0</v>
       </c>
       <c r="P32" s="2">
         <v>515.0</v>
       </c>
       <c r="Q32" s="2">
-        <v>46.0</v>
+        <v>45.0</v>
       </c>
       <c r="R32" s="2">
         <v>17.0</v>
@@ -3519,13 +3519,13 @@
         <v>1100.0</v>
       </c>
       <c r="O45" s="2">
-        <v>519.0</v>
+        <v>527.0</v>
       </c>
       <c r="P45" s="2">
         <v>544.0</v>
       </c>
       <c r="Q45" s="2">
-        <v>37.0</v>
+        <v>29.0</v>
       </c>
       <c r="R45" s="2">
         <v>51.0</v>
@@ -3661,10 +3661,10 @@
         <v>759.0</v>
       </c>
       <c r="O47" s="2">
-        <v>405.0</v>
+        <v>408.0</v>
       </c>
       <c r="P47" s="2">
-        <v>336.0</v>
+        <v>333.0</v>
       </c>
       <c r="Q47" s="2">
         <v>18.0</v>
@@ -3803,13 +3803,13 @@
         <v>1354.0</v>
       </c>
       <c r="O49" s="2">
-        <v>802.0</v>
+        <v>805.0</v>
       </c>
       <c r="P49" s="2">
-        <v>538.0</v>
+        <v>540.0</v>
       </c>
       <c r="Q49" s="2">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="R49" s="2">
         <v>68.0</v>
@@ -5066,7 +5066,7 @@
         <v>1129.0</v>
       </c>
       <c r="J67" s="2">
-        <v>1049.0</v>
+        <v>1048.0</v>
       </c>
       <c r="K67" s="2">
         <v>1.0</v>
@@ -5078,13 +5078,13 @@
         <v>0.0</v>
       </c>
       <c r="N67" s="2">
-        <v>1049.0</v>
+        <v>1048.0</v>
       </c>
       <c r="O67" s="2">
         <v>501.0</v>
       </c>
       <c r="P67" s="2">
-        <v>512.0</v>
+        <v>511.0</v>
       </c>
       <c r="Q67" s="2">
         <v>36.0</v>
@@ -5093,7 +5093,7 @@
         <v>60.0</v>
       </c>
       <c r="S67" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="T67" s="2">
         <v>0.0</v>
@@ -5105,7 +5105,7 @@
         <v>0.0</v>
       </c>
       <c r="W67" s="2">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
@@ -8545,7 +8545,7 @@
         <v>1148.0</v>
       </c>
       <c r="J116" s="2">
-        <v>948.0</v>
+        <v>990.0</v>
       </c>
       <c r="K116" s="2">
         <v>1.0</v>
@@ -8557,13 +8557,13 @@
         <v>1.0</v>
       </c>
       <c r="N116" s="2">
-        <v>947.0</v>
+        <v>989.0</v>
       </c>
       <c r="O116" s="2">
-        <v>136.0</v>
+        <v>149.0</v>
       </c>
       <c r="P116" s="2">
-        <v>415.0</v>
+        <v>444.0</v>
       </c>
       <c r="Q116" s="2">
         <v>397.0</v>
@@ -8572,7 +8572,7 @@
         <v>11.0</v>
       </c>
       <c r="S116" s="2">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="T116" s="2">
         <v>2.0</v>
@@ -8584,7 +8584,7 @@
         <v>0.0</v>
       </c>
       <c r="W116" s="2">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
@@ -9980,13 +9980,13 @@
         <v>1044.0</v>
       </c>
       <c r="O136" s="2">
-        <v>535.0</v>
+        <v>536.0</v>
       </c>
       <c r="P136" s="2">
         <v>468.0</v>
       </c>
       <c r="Q136" s="2">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="R136" s="2">
         <v>36.0</v>
@@ -10462,7 +10462,7 @@
         <v>1469.0</v>
       </c>
       <c r="J143" s="2">
-        <v>1417.0</v>
+        <v>1421.0</v>
       </c>
       <c r="K143" s="2">
         <v>1.0</v>
@@ -10474,19 +10474,19 @@
         <v>0.0</v>
       </c>
       <c r="N143" s="2">
-        <v>1417.0</v>
+        <v>1421.0</v>
       </c>
       <c r="O143" s="2">
-        <v>819.0</v>
+        <v>821.0</v>
       </c>
       <c r="P143" s="2">
-        <v>597.0</v>
+        <v>599.0</v>
       </c>
       <c r="Q143" s="2">
         <v>1.0</v>
       </c>
       <c r="R143" s="2">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="S143" s="2">
         <v>1.0</v>
@@ -10501,7 +10501,7 @@
         <v>0.0</v>
       </c>
       <c r="W143" s="2">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
@@ -10705,7 +10705,7 @@
         <v>45.0</v>
       </c>
       <c r="T146" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U146" s="2">
         <v>3.0</v>
@@ -10714,7 +10714,7 @@
         <v>1.0</v>
       </c>
       <c r="W146" s="2">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
@@ -10746,7 +10746,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>1047.0</v>
+        <v>1049.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -10758,10 +10758,10 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>1047.0</v>
+        <v>1049.0</v>
       </c>
       <c r="O147" s="2">
-        <v>532.0</v>
+        <v>534.0</v>
       </c>
       <c r="P147" s="2">
         <v>510.0</v>
@@ -10770,7 +10770,7 @@
         <v>5.0</v>
       </c>
       <c r="R147" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="S147" s="2">
         <v>3.0</v>
@@ -10785,7 +10785,7 @@
         <v>0.0</v>
       </c>
       <c r="W147" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
@@ -10817,7 +10817,7 @@
         <v>1269.0</v>
       </c>
       <c r="J148" s="2">
-        <v>1213.0</v>
+        <v>1215.0</v>
       </c>
       <c r="K148" s="2">
         <v>1.0</v>
@@ -10829,13 +10829,13 @@
         <v>0.0</v>
       </c>
       <c r="N148" s="2">
-        <v>1213.0</v>
+        <v>1215.0</v>
       </c>
       <c r="O148" s="2">
-        <v>627.0</v>
+        <v>628.0</v>
       </c>
       <c r="P148" s="2">
-        <v>568.0</v>
+        <v>569.0</v>
       </c>
       <c r="Q148" s="2">
         <v>18.0</v>
@@ -10844,7 +10844,7 @@
         <v>26.0</v>
       </c>
       <c r="S148" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="T148" s="2">
         <v>4.0</v>
@@ -10856,7 +10856,7 @@
         <v>0.0</v>
       </c>
       <c r="W148" s="2">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
@@ -10888,7 +10888,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" s="2">
-        <v>1087.0</v>
+        <v>1100.0</v>
       </c>
       <c r="K149" s="2">
         <v>1.0</v>
@@ -10900,16 +10900,16 @@
         <v>0.0</v>
       </c>
       <c r="N149" s="2">
-        <v>1087.0</v>
+        <v>1100.0</v>
       </c>
       <c r="O149" s="2">
-        <v>651.0</v>
+        <v>659.0</v>
       </c>
       <c r="P149" s="2">
-        <v>412.0</v>
+        <v>416.0</v>
       </c>
       <c r="Q149" s="2">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="R149" s="2">
         <v>57.0</v>
@@ -11030,7 +11030,7 @@
         <v>695.0</v>
       </c>
       <c r="J151" s="2">
-        <v>672.0</v>
+        <v>673.0</v>
       </c>
       <c r="K151" s="2">
         <v>1.0</v>
@@ -11042,10 +11042,10 @@
         <v>0.0</v>
       </c>
       <c r="N151" s="2">
-        <v>672.0</v>
+        <v>673.0</v>
       </c>
       <c r="O151" s="2">
-        <v>364.0</v>
+        <v>365.0</v>
       </c>
       <c r="P151" s="2">
         <v>307.0</v>
@@ -11054,7 +11054,7 @@
         <v>1.0</v>
       </c>
       <c r="R151" s="2">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="S151" s="2">
         <v>2.0</v>
@@ -11069,7 +11069,7 @@
         <v>0.0</v>
       </c>
       <c r="W151" s="2">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
@@ -11385,7 +11385,7 @@
         <v>1119.0</v>
       </c>
       <c r="J156" s="2">
-        <v>1067.0</v>
+        <v>1069.0</v>
       </c>
       <c r="K156" s="2">
         <v>1.0</v>
@@ -11397,16 +11397,16 @@
         <v>0.0</v>
       </c>
       <c r="N156" s="2">
-        <v>1067.0</v>
+        <v>1069.0</v>
       </c>
       <c r="O156" s="2">
-        <v>544.0</v>
+        <v>545.0</v>
       </c>
       <c r="P156" s="2">
         <v>520.0</v>
       </c>
       <c r="Q156" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R156" s="2">
         <v>32.0</v>
@@ -11740,7 +11740,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>1306.0</v>
+        <v>1308.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -11752,10 +11752,10 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>1306.0</v>
+        <v>1308.0</v>
       </c>
       <c r="O161" s="2">
-        <v>723.0</v>
+        <v>725.0</v>
       </c>
       <c r="P161" s="2">
         <v>560.0</v>
@@ -11764,7 +11764,7 @@
         <v>23.0</v>
       </c>
       <c r="R161" s="2">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="S161" s="2">
         <v>14.0</v>
@@ -11779,7 +11779,7 @@
         <v>0.0</v>
       </c>
       <c r="W161" s="2">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
@@ -13089,7 +13089,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" s="2">
-        <v>705.0</v>
+        <v>708.0</v>
       </c>
       <c r="K180" s="2">
         <v>1.0</v>
@@ -13101,13 +13101,13 @@
         <v>0.0</v>
       </c>
       <c r="N180" s="2">
-        <v>705.0</v>
+        <v>708.0</v>
       </c>
       <c r="O180" s="2">
-        <v>373.0</v>
+        <v>374.0</v>
       </c>
       <c r="P180" s="2">
-        <v>332.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q180" s="2">
         <v>0.0</v>
@@ -13116,7 +13116,7 @@
         <v>37.0</v>
       </c>
       <c r="S180" s="2">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="T180" s="2">
         <v>3.0</v>
@@ -13128,7 +13128,7 @@
         <v>0.0</v>
       </c>
       <c r="W180" s="2">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="181" ht="15.75" customHeight="1">
@@ -13728,7 +13728,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" s="2">
-        <v>1220.0</v>
+        <v>1223.0</v>
       </c>
       <c r="K189" s="2">
         <v>1.0</v>
@@ -13740,13 +13740,13 @@
         <v>0.0</v>
       </c>
       <c r="N189" s="2">
-        <v>1220.0</v>
+        <v>1223.0</v>
       </c>
       <c r="O189" s="2">
-        <v>514.0</v>
+        <v>515.0</v>
       </c>
       <c r="P189" s="2">
-        <v>424.0</v>
+        <v>426.0</v>
       </c>
       <c r="Q189" s="2">
         <v>282.0</v>
@@ -14027,13 +14027,13 @@
         <v>1284.0</v>
       </c>
       <c r="O193" s="2">
-        <v>491.0</v>
+        <v>500.0</v>
       </c>
       <c r="P193" s="2">
         <v>565.0</v>
       </c>
       <c r="Q193" s="2">
-        <v>228.0</v>
+        <v>219.0</v>
       </c>
       <c r="R193" s="2">
         <v>33.0</v>
@@ -14169,13 +14169,13 @@
         <v>538.0</v>
       </c>
       <c r="O195" s="2">
-        <v>234.0</v>
+        <v>235.0</v>
       </c>
       <c r="P195" s="2">
         <v>212.0</v>
       </c>
       <c r="Q195" s="2">
-        <v>92.0</v>
+        <v>91.0</v>
       </c>
       <c r="R195" s="2">
         <v>13.0</v>
@@ -14311,13 +14311,13 @@
         <v>1083.0</v>
       </c>
       <c r="O197" s="2">
-        <v>686.0</v>
+        <v>709.0</v>
       </c>
       <c r="P197" s="2">
-        <v>357.0</v>
+        <v>359.0</v>
       </c>
       <c r="Q197" s="2">
-        <v>40.0</v>
+        <v>15.0</v>
       </c>
       <c r="R197" s="2">
         <v>29.0</v>
@@ -14382,13 +14382,13 @@
         <v>1291.0</v>
       </c>
       <c r="O198" s="2">
-        <v>503.0</v>
+        <v>589.0</v>
       </c>
       <c r="P198" s="2">
-        <v>638.0</v>
+        <v>637.0</v>
       </c>
       <c r="Q198" s="2">
-        <v>150.0</v>
+        <v>65.0</v>
       </c>
       <c r="R198" s="2">
         <v>52.0</v>
@@ -15858,7 +15858,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>1296.0</v>
+        <v>1317.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15870,13 +15870,13 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>1296.0</v>
+        <v>1317.0</v>
       </c>
       <c r="O219" s="2">
-        <v>358.0</v>
+        <v>371.0</v>
       </c>
       <c r="P219" s="2">
-        <v>551.0</v>
+        <v>559.0</v>
       </c>
       <c r="Q219" s="2">
         <v>387.0</v>
@@ -15885,19 +15885,19 @@
         <v>34.0</v>
       </c>
       <c r="S219" s="2">
-        <v>73.0</v>
+        <v>76.0</v>
       </c>
       <c r="T219" s="2">
         <v>4.0</v>
       </c>
       <c r="U219" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="V219" s="2">
         <v>0.0</v>
       </c>
       <c r="W219" s="2">
-        <v>112.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
@@ -15944,13 +15944,13 @@
         <v>767.0</v>
       </c>
       <c r="O220" s="2">
-        <v>204.0</v>
+        <v>210.0</v>
       </c>
       <c r="P220" s="2">
         <v>343.0</v>
       </c>
       <c r="Q220" s="2">
-        <v>220.0</v>
+        <v>214.0</v>
       </c>
       <c r="R220" s="2">
         <v>16.0</v>
@@ -16086,13 +16086,13 @@
         <v>1012.0</v>
       </c>
       <c r="O222" s="2">
-        <v>407.0</v>
+        <v>447.0</v>
       </c>
       <c r="P222" s="2">
-        <v>459.0</v>
+        <v>469.0</v>
       </c>
       <c r="Q222" s="2">
-        <v>146.0</v>
+        <v>96.0</v>
       </c>
       <c r="R222" s="2">
         <v>19.0</v>
@@ -16142,7 +16142,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" s="2">
-        <v>1127.0</v>
+        <v>1138.0</v>
       </c>
       <c r="K223" s="2">
         <v>1.0</v>
@@ -16154,13 +16154,13 @@
         <v>2.0</v>
       </c>
       <c r="N223" s="2">
-        <v>1125.0</v>
+        <v>1136.0</v>
       </c>
       <c r="O223" s="2">
-        <v>169.0</v>
+        <v>177.0</v>
       </c>
       <c r="P223" s="2">
-        <v>317.0</v>
+        <v>320.0</v>
       </c>
       <c r="Q223" s="2">
         <v>641.0</v>
@@ -16169,10 +16169,10 @@
         <v>78.0</v>
       </c>
       <c r="S223" s="2">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="T223" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="U223" s="2">
         <v>0.0</v>
@@ -16181,7 +16181,7 @@
         <v>0.0</v>
       </c>
       <c r="W223" s="2">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
@@ -16213,7 +16213,7 @@
         <v>766.0</v>
       </c>
       <c r="J224" s="2">
-        <v>698.0</v>
+        <v>699.0</v>
       </c>
       <c r="K224" s="2">
         <v>1.0</v>
@@ -16225,10 +16225,10 @@
         <v>0.0</v>
       </c>
       <c r="N224" s="2">
-        <v>698.0</v>
+        <v>699.0</v>
       </c>
       <c r="O224" s="2">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="P224" s="2">
         <v>38.0</v>
@@ -16497,7 +16497,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" s="2">
-        <v>1296.0</v>
+        <v>1336.0</v>
       </c>
       <c r="K228" s="2">
         <v>1.0</v>
@@ -16509,22 +16509,22 @@
         <v>0.0</v>
       </c>
       <c r="N228" s="2">
-        <v>1296.0</v>
+        <v>1336.0</v>
       </c>
       <c r="O228" s="2">
-        <v>458.0</v>
+        <v>478.0</v>
       </c>
       <c r="P228" s="2">
-        <v>492.0</v>
+        <v>509.0</v>
       </c>
       <c r="Q228" s="2">
-        <v>346.0</v>
+        <v>349.0</v>
       </c>
       <c r="R228" s="2">
-        <v>38.0</v>
+        <v>43.0</v>
       </c>
       <c r="S228" s="2">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="T228" s="2">
         <v>0.0</v>
@@ -16536,7 +16536,7 @@
         <v>0.0</v>
       </c>
       <c r="W228" s="2">
-        <v>57.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
@@ -16639,7 +16639,7 @@
         <v>934.0</v>
       </c>
       <c r="J230" s="2">
-        <v>841.0</v>
+        <v>857.0</v>
       </c>
       <c r="K230" s="2">
         <v>1.0</v>
@@ -16651,25 +16651,25 @@
         <v>0.0</v>
       </c>
       <c r="N230" s="2">
-        <v>841.0</v>
+        <v>857.0</v>
       </c>
       <c r="O230" s="2">
-        <v>317.0</v>
+        <v>325.0</v>
       </c>
       <c r="P230" s="2">
-        <v>326.0</v>
+        <v>332.0</v>
       </c>
       <c r="Q230" s="2">
-        <v>198.0</v>
+        <v>200.0</v>
       </c>
       <c r="R230" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="S230" s="2">
-        <v>18.0</v>
+        <v>26.0</v>
       </c>
       <c r="T230" s="2">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="U230" s="2">
         <v>0.0</v>
@@ -16678,7 +16678,7 @@
         <v>0.0</v>
       </c>
       <c r="W230" s="2">
-        <v>39.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="231" ht="15.75" customHeight="1">
@@ -16710,7 +16710,7 @@
         <v>1070.0</v>
       </c>
       <c r="J231" s="2">
-        <v>920.0</v>
+        <v>922.0</v>
       </c>
       <c r="K231" s="2">
         <v>1.0</v>
@@ -16722,10 +16722,10 @@
         <v>0.0</v>
       </c>
       <c r="N231" s="2">
-        <v>920.0</v>
+        <v>922.0</v>
       </c>
       <c r="O231" s="2">
-        <v>492.0</v>
+        <v>494.0</v>
       </c>
       <c r="P231" s="2">
         <v>405.0</v>
@@ -16737,7 +16737,7 @@
         <v>14.0</v>
       </c>
       <c r="S231" s="2">
-        <v>128.0</v>
+        <v>126.0</v>
       </c>
       <c r="T231" s="2">
         <v>5.0</v>
@@ -16749,7 +16749,7 @@
         <v>0.0</v>
       </c>
       <c r="W231" s="2">
-        <v>150.0</v>
+        <v>148.0</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
@@ -16781,7 +16781,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" s="2">
-        <v>1116.0</v>
+        <v>1119.0</v>
       </c>
       <c r="K232" s="2">
         <v>1.0</v>
@@ -16793,10 +16793,10 @@
         <v>0.0</v>
       </c>
       <c r="N232" s="2">
-        <v>1116.0</v>
+        <v>1119.0</v>
       </c>
       <c r="O232" s="2">
-        <v>204.0</v>
+        <v>207.0</v>
       </c>
       <c r="P232" s="2">
         <v>231.0</v>
@@ -16805,10 +16805,10 @@
         <v>681.0</v>
       </c>
       <c r="R232" s="2">
-        <v>58.0</v>
+        <v>62.0</v>
       </c>
       <c r="S232" s="2">
-        <v>106.0</v>
+        <v>181.0</v>
       </c>
       <c r="T232" s="2">
         <v>0.0</v>
@@ -16820,7 +16820,7 @@
         <v>0.0</v>
       </c>
       <c r="W232" s="2">
-        <v>171.0</v>
+        <v>250.0</v>
       </c>
     </row>
     <row r="233" ht="15.75" customHeight="1">
